--- a/database/temp.xlsx
+++ b/database/temp.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User Vinatech.DESKTOP-RJJSEQU\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User Vinatech.DESKTOP-RJJSEQU\Desktop\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{957EFDC3-455B-4A3D-8E73-B82D4AFD9C16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45954CE3-CB83-4D9A-9F6E-D1A3F172E13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3A47A83A-EDBF-491B-87BA-CC4E501F318B}"/>
   </bookViews>
@@ -36,12 +36,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="78">
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Calibri"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="79">
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Mã nguyên liệu</t>
     </r>
@@ -51,6 +52,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Tên sản phẩm</t>
     </r>
@@ -60,6 +62,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Tên nguyên liệuL</t>
     </r>
@@ -69,6 +72,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>MMExtText01</t>
     </r>
@@ -78,6 +82,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>AltMaterialCode</t>
     </r>
@@ -87,6 +92,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Mã loại NVL</t>
     </r>
@@ -96,6 +102,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Loại NVL cơ bản</t>
     </r>
@@ -105,6 +112,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Tên loại NVL</t>
     </r>
@@ -114,6 +122,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Mã nhóm sản phẩm</t>
     </r>
@@ -123,6 +132,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Tên nhóm sản phẩm</t>
     </r>
@@ -132,6 +142,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Mô tả nhóm sphẩm</t>
     </r>
@@ -141,6 +152,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Đơn vị</t>
     </r>
@@ -150,6 +162,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Slg cơ bản</t>
     </r>
@@ -159,6 +172,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Đặc điểm nguyên liệu</t>
     </r>
@@ -168,6 +182,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Chi tiết đặc điểm nguyên liệu</t>
     </r>
@@ -177,6 +192,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Nguồn NVL</t>
     </r>
@@ -186,6 +202,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Độ dày NVL</t>
     </r>
@@ -195,6 +212,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Ngày trung bình</t>
     </r>
@@ -204,6 +222,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>IsDelegate</t>
     </r>
@@ -213,6 +232,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Sxuất nội bộ</t>
     </r>
@@ -222,6 +242,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Có k/hoạch sxuất</t>
     </r>
@@ -231,6 +252,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Đang mua</t>
     </r>
@@ -240,6 +262,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Đang đặt hàng</t>
     </r>
@@ -249,6 +272,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>IsUseFlush</t>
     </r>
@@ -258,6 +282,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>IsUseBackFlush</t>
     </r>
@@ -267,6 +292,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Loại hình mua</t>
     </r>
@@ -276,6 +302,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Đang đóng</t>
     </r>
@@ -285,6 +312,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>BeforeMaterialCode</t>
     </r>
@@ -294,6 +322,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>RequestGrDay</t>
     </r>
@@ -303,6 +332,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Chi phí cơ bản</t>
     </r>
@@ -312,6 +342,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>BasicCostPriceVVT</t>
     </r>
@@ -321,6 +352,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>SlgĐóngGóiCơBản</t>
     </r>
@@ -330,6 +362,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Kế hoạch sxuất tối đa</t>
     </r>
@@ -339,6 +372,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>BasicRoutingCode</t>
     </r>
@@ -348,6 +382,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>BasicRoutingName</t>
     </r>
@@ -357,6 +392,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>MMExtText02</t>
     </r>
@@ -366,6 +402,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>MMExtText03</t>
     </r>
@@ -375,6 +412,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>MMExtText04</t>
     </r>
@@ -384,6 +422,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>MMExtText06</t>
     </r>
@@ -393,6 +432,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>MMExtInt01</t>
     </r>
@@ -402,6 +442,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>DangerMaterialYn</t>
     </r>
@@ -411,6 +452,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>위험물구분</t>
     </r>
@@ -420,6 +462,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Mục đích</t>
     </r>
@@ -429,6 +472,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>성상</t>
     </r>
@@ -438,6 +482,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>보관방법</t>
     </r>
@@ -447,6 +492,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>화학물질명</t>
     </r>
@@ -456,6 +502,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Cas No.</t>
     </r>
@@ -465,6 +512,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>함량</t>
     </r>
@@ -474,6 +522,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>DangerClassificationDetail</t>
     </r>
@@ -483,6 +532,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>DesignQty</t>
     </r>
@@ -570,6 +620,9 @@
   </si>
   <si>
     <t>ANODE FOIL U170 4.9VFS 3.5mm</t>
+  </si>
+  <si>
+    <t>16RL1800ME16XXB001</t>
   </si>
 </sst>
 </file>
@@ -589,22 +642,26 @@
       <sz val="9"/>
       <color rgb="FF000080"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000080"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF800000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1000,7 +1057,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20C9BCFC-8DDE-4E44-8A9A-DAA235070715}">
-  <dimension ref="A1:AX10"/>
+  <dimension ref="A1:AX11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.88671875" bestFit="1" customWidth="1"/>
@@ -2047,6 +2104,92 @@
       <c r="AW10" s="4"/>
       <c r="AX10" s="4"/>
     </row>
+    <row r="11" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="V11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="W11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="X11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="4"/>
+      <c r="AA11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="4"/>
+      <c r="AC11" s="5"/>
+      <c r="AD11" s="4"/>
+      <c r="AE11" s="4"/>
+      <c r="AF11" s="6"/>
+      <c r="AG11" s="4"/>
+      <c r="AH11" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI11" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AJ11" s="4"/>
+      <c r="AK11" s="4"/>
+      <c r="AL11" s="4"/>
+      <c r="AM11" s="4"/>
+      <c r="AN11" s="4"/>
+      <c r="AO11" s="4"/>
+      <c r="AP11" s="4"/>
+      <c r="AQ11" s="4"/>
+      <c r="AR11" s="4"/>
+      <c r="AS11" s="4"/>
+      <c r="AT11" s="4"/>
+      <c r="AU11" s="4"/>
+      <c r="AV11" s="4"/>
+      <c r="AW11" s="4"/>
+      <c r="AX11" s="4"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/database/temp.xlsx
+++ b/database/temp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User Vinatech.DESKTOP-RJJSEQU\Desktop\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1656CF7-EAF6-403C-A7C1-7FA282BA65E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B13E81E-6B91-43C6-ABC0-B499E757A061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3A47A83A-EDBF-491B-87BA-CC4E501F318B}"/>
   </bookViews>
@@ -1105,7 +1105,7 @@
     <col min="31" max="31" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="13.21875" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="20.33203125" bestFit="1" customWidth="1"/>
     <col min="36" max="39" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="9" bestFit="1" customWidth="1"/>
